--- a/reports/telegram/aegis_daily_2026-09-14.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-14.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="AV29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="W33" s="3" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>1</v>
@@ -5854,11 +5854,11 @@
         <v>3</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>13.77</v>
+        <v>13.79</v>
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AV36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="W40" s="3" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>2</v>
@@ -6986,11 +6986,11 @@
         <v>3</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>15.48</v>
+        <v>15.46</v>
       </c>
       <c r="AV40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AV41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AV44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="AV45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="AV47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="AV48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AV49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="AV50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AV51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="AV52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AV53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="AV54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="AV55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="AV56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="AV57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="AV58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="AV59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="AV60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="AV61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AV62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="AV63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="AV64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="AV65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="AV66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AV67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="AV68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="AV69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -11672,19 +11672,19 @@
       </c>
       <c r="AV70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>R2-ASIANPAINT-IND-20260914-b2f056</t>
+          <t>R2-JKCEMENT-IND-20260914-b2b09a</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT_IND_20260914</t>
+          <t>JKCEMENT_IND_20260914</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr"/>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="Q71" s="3" t="n">
         <v>-1.8</v>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="T71" s="3" t="inlineStr"/>
       <c r="U71" s="3" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="V71" s="3" t="inlineStr">
         <is>
@@ -11770,40 +11770,40 @@
       </c>
       <c r="AB71" s="3" t="inlineStr"/>
       <c r="AC71" s="3" t="n">
-        <v>2461</v>
+        <v>4863</v>
       </c>
       <c r="AD71" s="3" t="n">
-        <v>2461</v>
+        <v>4863</v>
       </c>
       <c r="AE71" s="3" t="n">
-        <v>2436.39</v>
+        <v>4814.37</v>
       </c>
       <c r="AF71" s="3" t="n">
-        <v>2485.61</v>
+        <v>4911.63</v>
       </c>
       <c r="AG71" s="3" t="n">
-        <v>2337.95</v>
+        <v>4619.85</v>
       </c>
       <c r="AH71" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>2657.88</v>
+        <v>5252.04</v>
       </c>
       <c r="AJ71" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>2830.15</v>
+        <v>5592.45</v>
       </c>
       <c r="AL71" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM71" s="3" t="n">
-        <v>2469.1</v>
+        <v>4996</v>
       </c>
       <c r="AN71" s="3" t="n">
-        <v>-0.33</v>
+        <v>-2.66</v>
       </c>
       <c r="AO71" s="3" t="n">
         <v>0</v>
@@ -11816,29 +11816,29 @@
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>Mean Reversion · Value · Momentum</t>
+          <t>Mean Reversion · Growth · Quality</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr"/>
       <c r="AT71" s="3" t="inlineStr"/>
       <c r="AU71" s="3" t="n">
-        <v>21.62</v>
+        <v>21.64</v>
       </c>
       <c r="AV71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>R2-JKCEMENT-IND-20260914-b2b09a</t>
+          <t>R2-ASIANPAINT-IND-20260914-b2f056</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>JKCEMENT_IND_20260914</t>
+          <t>ASIANPAINT_IND_20260914</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
         </is>
       </c>
       <c r="P72" s="3" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="Q72" s="3" t="n">
         <v>-1.8</v>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="T72" s="3" t="inlineStr"/>
       <c r="U72" s="3" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="V72" s="3" t="inlineStr">
         <is>
@@ -11924,40 +11924,40 @@
       </c>
       <c r="AB72" s="3" t="inlineStr"/>
       <c r="AC72" s="3" t="n">
-        <v>4863</v>
+        <v>2461</v>
       </c>
       <c r="AD72" s="3" t="n">
-        <v>4863</v>
+        <v>2461</v>
       </c>
       <c r="AE72" s="3" t="n">
-        <v>4814.37</v>
+        <v>2436.39</v>
       </c>
       <c r="AF72" s="3" t="n">
-        <v>4911.63</v>
+        <v>2485.61</v>
       </c>
       <c r="AG72" s="3" t="n">
-        <v>4619.85</v>
+        <v>2337.95</v>
       </c>
       <c r="AH72" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>5252.04</v>
+        <v>2657.88</v>
       </c>
       <c r="AJ72" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>5592.45</v>
+        <v>2830.15</v>
       </c>
       <c r="AL72" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM72" s="3" t="n">
-        <v>4996</v>
+        <v>2469.1</v>
       </c>
       <c r="AN72" s="3" t="n">
-        <v>-2.66</v>
+        <v>-0.33</v>
       </c>
       <c r="AO72" s="3" t="n">
         <v>0</v>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>Mean Reversion · Growth · Quality</t>
+          <t>Mean Reversion · Value · Momentum</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr"/>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="AV72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="AV73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="AV74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="AV75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AV76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -12758,11 +12758,11 @@
       <c r="AS77" s="3" t="inlineStr"/>
       <c r="AT77" s="3" t="inlineStr"/>
       <c r="AU77" s="3" t="n">
-        <v>22.25</v>
+        <v>22.19</v>
       </c>
       <c r="AV77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="AV78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AV79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AV80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="AV81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="AV82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="AV83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -13844,7 +13844,7 @@
       </c>
       <c r="AV84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="AV85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="AV86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="AV87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="AV88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="AV89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="AV90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="AV91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AV92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="AV93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AV94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="AV95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AV96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AV97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="AV98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="AV99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="AV100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="AV101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -16624,7 +16624,7 @@
       </c>
       <c r="AV102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="AV103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -16932,7 +16932,7 @@
       </c>
       <c r="AV104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="AV105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AV106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AV107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -17544,11 +17544,11 @@
       <c r="AS108" s="3" t="inlineStr"/>
       <c r="AT108" s="3" t="inlineStr"/>
       <c r="AU108" s="3" t="n">
-        <v>25.83</v>
+        <v>25.85</v>
       </c>
       <c r="AV108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -17706,11 +17706,11 @@
       <c r="AS109" s="3" t="inlineStr"/>
       <c r="AT109" s="3" t="inlineStr"/>
       <c r="AU109" s="3" t="n">
-        <v>25.84</v>
+        <v>25.87</v>
       </c>
       <c r="AV109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="AV110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="AV111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -18154,7 +18154,7 @@
       </c>
       <c r="AV112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -18308,7 +18308,7 @@
       </c>
       <c r="AV113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -18462,7 +18462,7 @@
       </c>
       <c r="AV114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -18616,7 +18616,7 @@
       </c>
       <c r="AV115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -18770,7 +18770,7 @@
       </c>
       <c r="AV116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="AV117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -19082,7 +19082,7 @@
       </c>
       <c r="AV118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="AV119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="AV120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="AV121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -19710,7 +19710,7 @@
       </c>
       <c r="AV122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="AV123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="AV124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -20172,7 +20172,7 @@
       </c>
       <c r="AV125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -20330,7 +20330,7 @@
       </c>
       <c r="AV126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -20412,7 +20412,7 @@
         </is>
       </c>
       <c r="W127" s="3" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="X127" s="3" t="n">
         <v>1</v>
@@ -20480,11 +20480,11 @@
       <c r="AS127" s="3" t="inlineStr"/>
       <c r="AT127" s="3" t="inlineStr"/>
       <c r="AU127" s="3" t="n">
-        <v>27.78</v>
+        <v>27.8</v>
       </c>
       <c r="AV127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="AV128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="AV129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -20946,7 +20946,7 @@
       </c>
       <c r="AV130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -21100,19 +21100,19 @@
       </c>
       <c r="AV131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>R2-MAXHEALTH-IND-20260914-352d4c</t>
+          <t>R2-BOSCHLTD-IND-20260914-c5a8fb</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH_IND_20260914</t>
+          <t>BOSCHLTD_IND_20260914</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr"/>
@@ -21157,7 +21157,7 @@
         </is>
       </c>
       <c r="P132" s="3" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="Q132" s="3" t="n">
         <v>-1.8</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="T132" s="3" t="inlineStr"/>
       <c r="U132" s="3" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="V132" s="3" t="inlineStr">
         <is>
@@ -21198,40 +21198,40 @@
       </c>
       <c r="AB132" s="3" t="inlineStr"/>
       <c r="AC132" s="3" t="n">
-        <v>1026.8</v>
+        <v>48405</v>
       </c>
       <c r="AD132" s="3" t="n">
-        <v>1026.8</v>
+        <v>48405</v>
       </c>
       <c r="AE132" s="3" t="n">
-        <v>1016.53</v>
+        <v>47920.95</v>
       </c>
       <c r="AF132" s="3" t="n">
-        <v>1037.07</v>
+        <v>48889.05</v>
       </c>
       <c r="AG132" s="3" t="n">
-        <v>975.46</v>
+        <v>45984.75</v>
       </c>
       <c r="AH132" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI132" s="3" t="n">
-        <v>1108.94</v>
+        <v>52277.4</v>
       </c>
       <c r="AJ132" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK132" s="3" t="n">
-        <v>1180.82</v>
+        <v>55665.75</v>
       </c>
       <c r="AL132" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM132" s="3" t="n">
-        <v>1038.6</v>
+        <v>48675</v>
       </c>
       <c r="AN132" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.55</v>
       </c>
       <c r="AO132" s="3" t="n">
         <v>0</v>
@@ -21244,29 +21244,29 @@
       </c>
       <c r="AR132" s="3" t="inlineStr">
         <is>
-          <t>Value · Momentum · Mean Reversion</t>
+          <t>Mean Reversion · Momentum · Value</t>
         </is>
       </c>
       <c r="AS132" s="3" t="inlineStr"/>
       <c r="AT132" s="3" t="inlineStr"/>
       <c r="AU132" s="3" t="n">
-        <v>28.43</v>
+        <v>28.4</v>
       </c>
       <c r="AV132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>R2-BOSCHLTD-IND-20260914-c5a8fb</t>
+          <t>R2-MAXHEALTH-IND-20260914-352d4c</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>BOSCHLTD_IND_20260914</t>
+          <t>MAXHEALTH_IND_20260914</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -21286,7 +21286,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr"/>
@@ -21311,7 +21311,7 @@
         </is>
       </c>
       <c r="P133" s="3" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="Q133" s="3" t="n">
         <v>-1.8</v>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="T133" s="3" t="inlineStr"/>
       <c r="U133" s="3" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="V133" s="3" t="inlineStr">
         <is>
@@ -21352,40 +21352,40 @@
       </c>
       <c r="AB133" s="3" t="inlineStr"/>
       <c r="AC133" s="3" t="n">
-        <v>48405</v>
+        <v>1026.8</v>
       </c>
       <c r="AD133" s="3" t="n">
-        <v>48405</v>
+        <v>1026.8</v>
       </c>
       <c r="AE133" s="3" t="n">
-        <v>47920.95</v>
+        <v>1016.53</v>
       </c>
       <c r="AF133" s="3" t="n">
-        <v>48889.05</v>
+        <v>1037.07</v>
       </c>
       <c r="AG133" s="3" t="n">
-        <v>45984.75</v>
+        <v>975.46</v>
       </c>
       <c r="AH133" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI133" s="3" t="n">
-        <v>52277.4</v>
+        <v>1108.94</v>
       </c>
       <c r="AJ133" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK133" s="3" t="n">
-        <v>55665.75</v>
+        <v>1180.82</v>
       </c>
       <c r="AL133" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM133" s="3" t="n">
-        <v>48675</v>
+        <v>1038.6</v>
       </c>
       <c r="AN133" s="3" t="n">
-        <v>-0.55</v>
+        <v>-1.14</v>
       </c>
       <c r="AO133" s="3" t="n">
         <v>0</v>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="AR133" s="3" t="inlineStr">
         <is>
-          <t>Mean Reversion · Momentum · Value</t>
+          <t>Value · Momentum · Mean Reversion</t>
         </is>
       </c>
       <c r="AS133" s="3" t="inlineStr"/>
@@ -21408,7 +21408,7 @@
       </c>
       <c r="AV133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -21562,7 +21562,7 @@
       </c>
       <c r="AV134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -21728,7 +21728,7 @@
       </c>
       <c r="AV135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="AV136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -22032,11 +22032,11 @@
       <c r="AS137" s="3" t="inlineStr"/>
       <c r="AT137" s="3" t="inlineStr"/>
       <c r="AU137" s="3" t="n">
-        <v>29.16</v>
+        <v>29.18</v>
       </c>
       <c r="AV137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -22190,7 +22190,7 @@
       </c>
       <c r="AV138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -22344,7 +22344,7 @@
       </c>
       <c r="AV139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -22498,7 +22498,7 @@
       </c>
       <c r="AV140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -22652,7 +22652,7 @@
       </c>
       <c r="AV141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -22810,7 +22810,7 @@
       </c>
       <c r="AV142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -22964,7 +22964,7 @@
       </c>
       <c r="AV143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -23118,7 +23118,7 @@
       </c>
       <c r="AV144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="AV145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -23426,7 +23426,7 @@
       </c>
       <c r="AV146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -23580,7 +23580,7 @@
       </c>
       <c r="AV147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -23734,7 +23734,7 @@
       </c>
       <c r="AV148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -23884,11 +23884,11 @@
       <c r="AS149" s="3" t="inlineStr"/>
       <c r="AT149" s="3" t="inlineStr"/>
       <c r="AU149" s="3" t="n">
-        <v>30.4</v>
+        <v>30.44</v>
       </c>
       <c r="AV149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -24042,7 +24042,7 @@
       </c>
       <c r="AV150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="AV151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -24354,7 +24354,7 @@
       </c>
       <c r="AV152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -24508,7 +24508,7 @@
       </c>
       <c r="AV153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="AV154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -24816,7 +24816,7 @@
       </c>
       <c r="AV155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -24970,7 +24970,7 @@
       </c>
       <c r="AV156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -25124,7 +25124,7 @@
       </c>
       <c r="AV157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="AV158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -25436,7 +25436,7 @@
       </c>
       <c r="AV159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="AV160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -25744,7 +25744,7 @@
       </c>
       <c r="AV161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -25898,7 +25898,7 @@
       </c>
       <c r="AV162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="AV163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AV164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -26372,11 +26372,11 @@
       <c r="AS165" s="3" t="inlineStr"/>
       <c r="AT165" s="3" t="inlineStr"/>
       <c r="AU165" s="3" t="n">
-        <v>39.51</v>
+        <v>39.53</v>
       </c>
       <c r="AV165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="AV166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="AV167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -26866,7 +26866,7 @@
       </c>
       <c r="AV168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -27028,7 +27028,7 @@
       </c>
       <c r="AV169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -27186,7 +27186,7 @@
       </c>
       <c r="AV170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -27344,7 +27344,7 @@
       </c>
       <c r="AV171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -27502,7 +27502,7 @@
       </c>
       <c r="AV172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -27660,7 +27660,7 @@
       </c>
       <c r="AV173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -27818,7 +27818,7 @@
       </c>
       <c r="AV174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="AV175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -28142,7 +28142,7 @@
       </c>
       <c r="AV176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="AV177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -28458,7 +28458,7 @@
       </c>
       <c r="AV178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -28614,7 +28614,7 @@
       </c>
       <c r="AV179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="AV180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -28926,7 +28926,7 @@
       </c>
       <c r="AV181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -29082,7 +29082,7 @@
       </c>
       <c r="AV182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="AV183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07</t>
+          <t>2026-09-14 01:41</t>
         </is>
       </c>
     </row>
